--- a/帝国时代2决定版 文明联盟 骑射流最优研究顺序 By RemonBo.xlsx
+++ b/帝国时代2决定版 文明联盟 骑射流最优研究顺序 By RemonBo.xlsx
@@ -1020,9 +1020,9 @@
       </c>
     </row>
     <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>S</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -1047,164 +1047,164 @@
       </c>
     </row>
     <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>马扎尔</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>反曲弓（骑射手攻+1，射程+1）</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>射程提升</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>马扎尔</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>骑射手训练速度 +25%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>团队加成</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>训练速度提升，成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>鞑靼</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>骑射手视野 +2</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>团队加成</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>视野提升</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>马扎尔</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>反曲弓（骑射手攻+1，射程+1）</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>土耳其</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>西帕希骑兵（骑射手生命+20）</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>射程提升</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>生命值提升，抗打更久</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>马扎尔</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>骑射手训练速度 +25%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>团队加成</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>直接强化骑射手</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>日本</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>骑射手对远程攻+2（掷矛手除外）</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>攻击力提升，正面更硬</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>鞑靼</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>骑射手视野 +2</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>团队加成</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>视野提升</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>土耳其</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>西帕希骑兵（骑射手生命+20）</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>生命值提升，抗打更久</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>日本</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>骑射手对远程攻+2（掷矛手除外）</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>波斯</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>城堡时代可用帕提亚战术</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>攻击力提升</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>波斯</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>城堡时代可用帕提亚战术</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>直接强化骑射手</t>
+          <t>提前解锁，抢一个时代的节奏</t>
         </is>
       </c>
     </row>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>直接强化骑射手</t>
+          <t>训练速度提升，成型更快</t>
         </is>
       </c>
     </row>
@@ -1286,83 +1286,83 @@
       </c>
     </row>
     <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>鞑靼</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>扳指/帕提亚战术免费</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>免费获得，等于直接省下这笔支出</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>鞑靼</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>扳指/帕提亚战术免费</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>匈奴</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>骑射手城堡/帝王费用-10/20%</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>免费获得，等于直接省下这笔支出</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>匈奴</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>骑射手城堡/帝王费用-10/20%</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>契丹</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>重装骑射手城堡可升级，成本-50%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>降低费用，让该流派更快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>契丹</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>重装骑射手城堡可升级，成本-50%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>降低费用，让该流派更快成型</t>
+          <t>解锁额外单位或升级选项，本流派可用的兵种更多</t>
         </is>
       </c>
     </row>

--- a/帝国时代2决定版 文明联盟 骑射流最优研究顺序 By RemonBo.xlsx
+++ b/帝国时代2决定版 文明联盟 骑射流最优研究顺序 By RemonBo.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开局3免费位" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="后续2000金顺序" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="甲类·骑射手本体强化" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="乙类·费用与前置" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="乙类·减费用与资源效率" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="与骑射流无关·可跳过" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主选文明推荐" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全62文明总名次" sheetId="7" state="visible" r:id="rId7"/>
@@ -18,13 +18,13 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'开局3免费位'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'后续2000金顺序'!$A$1:$F$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'后续2000金顺序'!$A$1:$F$9</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'后续2000金顺序'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'甲类·骑射手本体强化'!$A$1:$E$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'甲类·骑射手本体强化'!$A$1:$E$13</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'甲类·骑射手本体强化'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'乙类·费用与前置'!$A$1:$E$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">'乙类·费用与前置'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'与骑射流无关·可跳过'!$A$1:$D$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'乙类·减费用与资源效率'!$A$1:$E$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'乙类·减费用与资源效率'!$1:$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'与骑射流无关·可跳过'!$A$1:$D$52</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'与骑射流无关·可跳过'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'主选文明推荐'!$A$1:$E$10</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'主选文明推荐'!$1:$1</definedName>
@@ -579,12 +579,12 @@
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>骑射手攻速+25%</t>
+          <t>骑射手攻速+25%；斥候/草原枪兵城堡/帝王生命+20/30%</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 1 / 弱 1）；骑射手科技树 13/14；缺 环甲；最直接一条：骑射手攻速+25%</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 1）；骑射手科技树 13/14；缺 环甲；最直接一条：骑射手攻速+25%</t>
         </is>
       </c>
     </row>
@@ -592,13 +592,13 @@
       <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>匈奴（备选）</t>
+          <t>土耳其（备选）</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr"/>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 1 条（强 1 / 弱 0）；骑射手科技树 13/14；缺 环甲；最直接一条：骑射手城堡/帝王费用-10/20%</t>
+          <t>备选：阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；骑射手科技树 14/14（无缺项）；最直接一条：西帕希骑兵（骑射手生命+20）</t>
         </is>
       </c>
     </row>
@@ -606,13 +606,13 @@
       <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>土耳其（备选）</t>
+          <t>日本（备选）</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr"/>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 1 条（强 1 / 弱 0）；骑射手科技树 14/14（无缺项）；最直接一条：西帕希骑兵（骑射手生命+20）</t>
+          <t>备选：阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；骑射手科技树 14/14（无缺项）；最直接一条：骑射手对远程攻+2（掷矛手除外）</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       <c r="C5" s="4" t="inlineStr"/>
       <c r="D5" s="4" t="inlineStr"/>
     </row>
-    <row r="6" ht="36" customHeight="1">
+    <row r="6" ht="51" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>第 2 位</t>
@@ -635,12 +635,12 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>反曲弓（骑射手攻+1，射程+1）；骑射手训练速度 +25%</t>
+          <t>科维尼安军队（马扎尔骠骑消耗额外食物而非黄金）；反曲弓（骑射手攻+1，射程+1）；骑射手训练速度 +25%</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 3 / 弱 0）；骑射手科技树 14/14（无缺项）；最直接一条：科维尼安军队（马扎尔骠骑消耗额外食物而非黄金）</t>
+          <t>阶段1·本体强化；原生条目 5 条（强 3 / 弱 0）；骑射手科技树 14/14（无缺项）；最直接一条：科维尼安军队（马扎尔骠骑消耗额外食物而非黄金）</t>
         </is>
       </c>
     </row>
@@ -648,13 +648,13 @@
       <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>契丹（备选）</t>
+          <t>波斯（备选）</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr"/>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 1 条（强 1 / 弱 0）；骑射手科技树 13/14；缺 血统；最直接一条：重装骑射手城堡可升级，成本-50%</t>
+          <t>备选：阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；骑射手科技树 13/14；缺 护腕；最直接一条：城堡时代可用帕提亚战术</t>
         </is>
       </c>
     </row>
@@ -662,13 +662,13 @@
       <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>日本（备选）</t>
+          <t>库曼（备选）</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr"/>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 1 条（强 1 / 弱 0）；骑射手科技树 14/14（无缺项）；最直接一条：骑射手对远程攻+2（掷矛手除外）</t>
+          <t>备选：阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；骑射手科技树 12/14；缺 驯马、护腕；最直接一条：大草原畜牧（斥候/草原枪兵/骑射手训练速度+100%）</t>
         </is>
       </c>
     </row>
@@ -691,12 +691,12 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>扳指/帕提亚战术免费；骑射手视野 +2</t>
+          <t>扳指/帕提亚战术免费；骑射手视野 +2；丝护甲（斥候/草原枪兵近战护甲+1/远程护甲+1）</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 2 / 弱 1）；骑射手科技树 14/14（无缺项）；最直接一条：扳指/帕提亚战术免费</t>
+          <t>阶段1·本体强化；原生条目 5 条（强 2 / 弱 1）；骑射手科技树 14/14（无缺项）；最直接一条：扳指/帕提亚战术免费</t>
         </is>
       </c>
     </row>
@@ -704,13 +704,13 @@
       <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>波斯（备选）</t>
+          <t>匈奴（备选）</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr"/>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 1 条（强 1 / 弱 0）；骑射手科技树 13/14；缺 护腕；最直接一条：城堡时代可用帕提亚战术</t>
+          <t>备选：阶段2·减费用；原生条目 2 条（强 1 / 弱 0）；骑射手科技树 13/14；缺 环甲；最直接一条：骑射手城堡/帝王费用-10/20%</t>
         </is>
       </c>
     </row>
@@ -718,13 +718,13 @@
       <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>库曼（备选）</t>
+          <t>契丹（备选）</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 1 条（强 1 / 弱 0）；骑射手科技树 12/14；缺 驯马、护腕；最直接一条：大草原畜牧（斥候/草原枪兵/骑射手训练速度+100%）</t>
+          <t>备选：阶段2·减费用；原生条目 2 条（强 1 / 弱 0）；骑射手科技树 13/14；缺 血统；最直接一条：重装骑射手城堡可升级，成本-50%</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -795,7 +795,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>匈奴</t>
+          <t>土耳其</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
@@ -805,17 +805,17 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>骑射手城堡/帝王费用-10/20%</t>
+          <t>西帕希骑兵（骑射手生命+20）</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>城堡时代起</t>
+          <t>无条件</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；骑射手科技树 13/14；缺 环甲；最直接一条：骑射手城堡/帝王费用-10/20%</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；骑射手科技树 14/14（无缺项）；最直接一条：西帕希骑兵（骑射手生命+20）</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>土耳其</t>
+          <t>日本</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
@@ -835,7 +835,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>西帕希骑兵（骑射手生命+20）</t>
+          <t>骑射手对远程攻+2（掷矛手除外）</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；骑射手科技树 14/14（无缺项）；最直接一条：西帕希骑兵（骑射手生命+20）</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；骑射手科技树 14/14（无缺项）；最直接一条：骑射手对远程攻+2（掷矛手除外）</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>契丹</t>
+          <t>波斯</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>重装骑射手城堡可升级，成本-50%</t>
+          <t>城堡时代可用帕提亚战术</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -875,17 +875,17 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；骑射手科技树 13/14；缺 血统；最直接一条：重装骑射手城堡可升级，成本-50%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；骑射手科技树 13/14；缺 护腕；最直接一条：城堡时代可用帕提亚战术</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="51" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>7</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>日本</t>
+          <t>库曼</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>骑射手对远程攻+2（掷矛手除外）</t>
+          <t>大草原畜牧（斥候/草原枪兵/骑射手训练速度+100%）</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；骑射手科技树 14/14（无缺项）；最直接一条：骑射手对远程攻+2（掷矛手除外）</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；骑射手科技树 12/14；缺 驯马、护腕；最直接一条：大草原畜牧（斥候/草原枪兵/骑射手训练速度+100%）</t>
         </is>
       </c>
     </row>
@@ -915,7 +915,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>波斯</t>
+          <t>匈奴</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -925,7 +925,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>城堡时代可用帕提亚战术</t>
+          <t>骑射手城堡/帝王费用-10/20%</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；骑射手科技树 13/14；缺 护腕；最直接一条：城堡时代可用帕提亚战术</t>
+          <t>阶段2·减费用；原生条目 2 条（强 1 / 弱 0）；骑射手科技树 13/14；缺 环甲；最直接一条：骑射手城堡/帝王费用-10/20%</t>
         </is>
       </c>
     </row>
@@ -945,7 +945,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>库曼</t>
+          <t>契丹</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -955,22 +955,82 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>大草原畜牧（斥候/草原枪兵/骑射手训练速度+100%）</t>
+          <t>重装骑射手城堡可升级，成本-50%</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
+          <t>城堡时代起</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>阶段2·减费用；原生条目 2 条（强 1 / 弱 0）；骑射手科技树 13/14；缺 血统；最直接一条：重装骑射手城堡可升级，成本-50%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="36" customHeight="1">
+      <c r="A8" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>高丽</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>弓兵护甲/塔升级免费（升级炮塔需要化学）</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
           <t>无条件</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；骑射手科技树 12/14；缺 驯马、护腕；最直接一条：大草原畜牧（斥候/草原枪兵/骑射手训练速度+100%）</t>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；骑射手科技树 12/14；缺 帕提亚战术、血统</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>葡萄牙</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>所有单位黄金费用-20%</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>无条件</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；骑射手科技树 11/14；缺 重装骑射手、骑射手、帕提亚战术</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F7"/>
+  <autoFilter ref="A1:F9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -982,7 +1042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1054,22 +1114,22 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>马扎尔</t>
+          <t>蒙古</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>反曲弓（骑射手攻+1，射程+1）</t>
+          <t>斥候/草原枪兵城堡/帝王生命+20/30%</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>独特科技</t>
+          <t>主要功能</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>射程提升</t>
+          <t>生命值提升，抗打更久</t>
         </is>
       </c>
     </row>
@@ -1086,17 +1146,17 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>骑射手训练速度 +25%</t>
+          <t>科维尼安军队（马扎尔骠骑消耗额外食物而非黄金）</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>团队加成</t>
+          <t>独特科技</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>训练速度提升，成型更快</t>
+          <t>资源产出/节省，加快成型</t>
         </is>
       </c>
     </row>
@@ -1108,135 +1168,243 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
+          <t>马扎尔</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>反曲弓（骑射手攻+1，射程+1）</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>射程提升</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>马扎尔</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>骑射手训练速度 +25%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>团队加成</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>训练速度提升，成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>鞑靼</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>扳指/帕提亚战术免费</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>免费获得，等于直接省下这笔支出</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>鞑靼</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>骑射手视野 +2</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>团队加成</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>视野提升</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>鞑靼</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>丝护甲（斥候/草原枪兵近战护甲+1/远程护甲+1）</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>护甲提升，减伤更耐打</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>土耳其</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>西帕希骑兵（骑射手生命+20）</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>生命值提升，抗打更久</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>日本</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>骑射手对远程攻+2（掷矛手除外）</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>攻击力提升，正面更硬</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>波斯</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>城堡时代可用帕提亚战术</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>提前解锁，抢一个时代的节奏</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>库曼</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>大草原畜牧（斥候/草原枪兵/骑射手训练速度+100%）</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>训练速度提升，成型更快</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E9"/>
+  <autoFilter ref="A1:E13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -1248,7 +1416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1286,19 +1454,19 @@
       </c>
     </row>
     <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="7" t="inlineStr">
-        <is>
-          <t>S</t>
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>鞑靼</t>
+          <t>匈奴</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>扳指/帕提亚战术免费</t>
+          <t>骑射手城堡/帝王费用-10/20%</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1308,24 +1476,24 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>免费获得，等于直接省下这笔支出</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="36" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>匈奴</t>
+          <t>契丹</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>骑射手城堡/帝王费用-10/20%</t>
+          <t>重装骑射手城堡可升级，成本-50%</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1335,39 +1503,66 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
+          <t>解锁额外单位或升级选项，本流派可用的兵种更多</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>高丽</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>弓兵护甲/塔升级免费（升级炮塔需要化学）</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>免费获得整条升级/科技，等于直接省下这笔研究支出</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>葡萄牙</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>所有单位黄金费用-20%</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
           <t>降低费用，让该流派更快成型</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>契丹</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>重装骑射手城堡可升级，成本-50%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>解锁额外单位或升级选项，本流派可用的兵种更多</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E4"/>
+  <autoFilter ref="A1:E5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -1379,7 +1574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D54"/>
+  <dimension ref="A1:D52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1677,12 +1872,12 @@
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>高丽</t>
+          <t>高棉</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>防御和海军文明</t>
+          <t>攻城武器和大象文明</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -1692,19 +1887,19 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>防御和海军文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「石矿工速度+20%」）</t>
+          <t>攻城武器和大象文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「无需建筑即可升时代/解锁建筑」）</t>
         </is>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>高棉</t>
+          <t>哥特</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>攻城武器和大象文明</t>
+          <t>步兵文明</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1714,19 +1909,19 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>攻城武器和大象文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「无需建筑即可升时代/解锁建筑」）</t>
+          <t>步兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「可立即研究织布机」）</t>
         </is>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>哥特</t>
+          <t>格鲁吉亚</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>步兵文明</t>
+          <t>防御和骑兵文明</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -1736,19 +1931,19 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>步兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「可立即研究织布机」）</t>
+          <t>防御和骑兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「开局有骡车」）</t>
         </is>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>格鲁吉亚</t>
+          <t>凯尔特</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>防御和骑兵文明</t>
+          <t>步兵和攻城武器文明</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -1758,19 +1953,19 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>防御和骑兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「开局有骡车」）</t>
+          <t>步兵和攻城武器文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「伐木工速度+15%」）</t>
         </is>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>凯尔特</t>
+          <t>立陶宛</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>步兵和攻城武器文明</t>
+          <t>骑兵和僧侣文明</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -1780,19 +1975,19 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>步兵和攻城武器文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「伐木工速度+15%」）</t>
+          <t>骑兵和僧侣文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「每座TC食物+100」）</t>
         </is>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>立陶宛</t>
+          <t>罗马</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>骑兵和僧侣文明</t>
+          <t>步兵和骑兵文明</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -1802,19 +1997,19 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>骑兵和僧侣文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「每座TC食物+100」）</t>
+          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「村民收集/建造/修理速度+5%」）</t>
         </is>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>罗马</t>
+          <t>马来</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明</t>
+          <t>海军文明</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -1824,19 +2019,19 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「村民收集/建造/修理速度+5%」）</t>
+          <t>海军文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「升时代速度+66%」）</t>
         </is>
       </c>
     </row>
     <row r="21" ht="36" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>马来</t>
+          <t>马里</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>海军文明</t>
+          <t>步兵文明</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -1846,19 +2041,19 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>海军文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「升时代速度+66%」）</t>
+          <t>步兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「建筑木材-15%」）</t>
         </is>
       </c>
     </row>
     <row r="22" ht="36" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>马里</t>
+          <t>马普切</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>步兵文明</t>
+          <t>骑兵与反制单位文明</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -1868,19 +2063,19 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>步兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「建筑木材-15%」）</t>
+          <t>骑兵与反制单位文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「采果工存食+25%」）</t>
         </is>
       </c>
     </row>
     <row r="23" ht="36" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>马普切</t>
+          <t>玛雅</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>骑兵与反制单位文明</t>
+          <t>弓兵文明</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -1890,19 +2085,19 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>骑兵与反制单位文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「采果工存食+25%」）</t>
+          <t>弓兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「开局村民+1，食物-50」）</t>
         </is>
       </c>
     </row>
     <row r="24" ht="36" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>玛雅</t>
+          <t>孟加拉</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>弓兵文明</t>
+          <t>象兵和海军文明</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -1912,19 +2107,19 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>弓兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「开局村民+1，食物-50」）</t>
+          <t>象兵和海军文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「升时代TC产生2村民」）</t>
         </is>
       </c>
     </row>
     <row r="25" ht="36" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>孟加拉</t>
+          <t>缅甸</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>象兵和海军文明</t>
+          <t>步兵和骑兵文明</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -1934,19 +2129,19 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>象兵和海军文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「升时代TC产生2村民」）</t>
+          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「伐木场科技免费」）</t>
         </is>
       </c>
     </row>
     <row r="26" ht="36" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>缅甸</t>
+          <t>穆伊斯卡</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明</t>
+          <t>弓兵与僧侣文明</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -1956,19 +2151,19 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「伐木场科技免费」）</t>
+          <t>弓兵与僧侣文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「升时代黄金-50%」）</t>
         </is>
       </c>
     </row>
     <row r="27" ht="36" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>穆伊斯卡</t>
+          <t>女真</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>弓兵与僧侣文明</t>
+          <t>骑兵和火药文明</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -1978,19 +2173,19 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>弓兵与僧侣文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「升时代黄金-50%」）</t>
+          <t>骑兵和火药文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「猎物/牲畜肉不腐烂」）</t>
         </is>
       </c>
     </row>
     <row r="28" ht="36" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>女真</t>
+          <t>瞿折罗</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>骑兵和火药文明</t>
+          <t>骑兵和骆驼文明</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -2000,19 +2195,19 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>骑兵和火药文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「猎物/牲畜肉不腐烂」）</t>
+          <t>骑兵和骆驼文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「开局2果树丛」）</t>
         </is>
       </c>
     </row>
     <row r="29" ht="36" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>葡萄牙</t>
+          <t>撒克逊人</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>海军和火药文明</t>
+          <t>步兵和防御文明</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -2022,19 +2217,19 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>海军和火药文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「采果工产食+木材」）</t>
+          <t>步兵和防御文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「磨坊/木料/采矿场建成后食物+35，石料+10」）</t>
         </is>
       </c>
     </row>
     <row r="30" ht="36" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>瞿折罗</t>
+          <t>萨拉森</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>骑兵和骆驼文明</t>
+          <t>骆驼和海军文明</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -2044,19 +2239,19 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>骑兵和骆驼文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「开局2果树丛」）</t>
+          <t>骆驼和海军文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「市场贸易税仅5%」）</t>
         </is>
       </c>
     </row>
     <row r="31" ht="36" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>撒克逊人</t>
+          <t>蜀</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>步兵和防御文明</t>
+          <t>弓兵和攻城文明</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -2066,19 +2261,19 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>步兵和防御文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「磨坊/木料/采矿场建成后食物+35，石料+10」）</t>
+          <t>弓兵和攻城文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「伐木工产木+食物」）</t>
         </is>
       </c>
     </row>
     <row r="32" ht="36" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>萨拉森</t>
+          <t>斯拉夫</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>骆驼和海军文明</t>
+          <t>步兵和攻城文明</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -2088,19 +2283,19 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>骆驼和海军文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「市场贸易税仅5%」）</t>
+          <t>步兵和攻城文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「农民工作速度+15%」）</t>
         </is>
       </c>
     </row>
     <row r="33" ht="36" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>蜀</t>
+          <t>条顿</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>弓兵和攻城文明</t>
+          <t>步兵和防御文明</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -2110,19 +2305,19 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>弓兵和攻城文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「伐木工产木+食物」）</t>
+          <t>步兵和防御文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「农田费用-40%」）</t>
         </is>
       </c>
     </row>
     <row r="34" ht="36" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>斯拉夫</t>
+          <t>图皮</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>步兵和攻城文明</t>
+          <t>弓兵与步兵文明</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -2132,19 +2327,19 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>步兵和攻城文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「农民工作速度+15%」）</t>
+          <t>弓兵与步兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「开局每种资源+25」）</t>
         </is>
       </c>
     </row>
     <row r="35" ht="36" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>条顿</t>
+          <t>瓦兰吉人</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>步兵和防御文明</t>
+          <t>骑兵和海军文明</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -2154,19 +2349,19 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>步兵和防御文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「农田费用-40%」）</t>
+          <t>骑兵和海军文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「牧羊/捕鱼/狩猎也产黄金」）</t>
         </is>
       </c>
     </row>
     <row r="36" ht="36" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>图皮</t>
+          <t>维京</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>弓兵与步兵文明</t>
+          <t>步兵和海军文明</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -2176,19 +2371,19 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>弓兵与步兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「开局每种资源+25」）</t>
+          <t>步兵和海军文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「独轮推车/手推车免费」）</t>
         </is>
       </c>
     </row>
     <row r="37" ht="36" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>瓦兰吉人</t>
+          <t>魏</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>骑兵和海军文明</t>
+          <t>骑兵文明</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -2198,14 +2393,14 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>骑兵和海军文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「牧羊/捕鱼/狩猎也产黄金」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「每研究一次经济升级免费获一村民」）</t>
         </is>
       </c>
     </row>
     <row r="38" ht="36" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>维京</t>
+          <t>吴</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2220,19 +2415,19 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>步兵和海军文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「独轮推车/手推车免费」）</t>
+          <t>步兵和海军文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「军事建筑/码头建成后食物+55」）</t>
         </is>
       </c>
     </row>
     <row r="39" ht="36" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>魏</t>
+          <t>西班牙</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>骑兵文明</t>
+          <t>火药和僧侣文明</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -2242,19 +2437,19 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「每研究一次经济升级免费获一村民」）</t>
+          <t>火药和僧侣文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「建筑工速度+30%」）</t>
         </is>
       </c>
     </row>
     <row r="40" ht="36" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>吴</t>
+          <t>西西里</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>步兵和海军文明</t>
+          <t>步兵和骑兵文明</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -2264,19 +2459,19 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>步兵和海军文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「军事建筑/码头建成后食物+55」）</t>
+          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「初始石料+100」）</t>
         </is>
       </c>
     </row>
     <row r="41" ht="36" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>西班牙</t>
+          <t>亚美尼亚</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>火药和僧侣文明</t>
+          <t>步兵和海军文明</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -2286,19 +2481,19 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>火药和僧侣文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「建筑工速度+30%」）</t>
+          <t>步兵和海军文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「骡车费用-25%」）</t>
         </is>
       </c>
     </row>
     <row r="42" ht="36" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>西西里</t>
+          <t>意大利</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明</t>
+          <t>弓兵和海军文明</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -2308,19 +2503,19 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「初始石料+100」）</t>
+          <t>弓兵和海军文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「升时代费用-15%」）</t>
         </is>
       </c>
     </row>
     <row r="43" ht="36" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>亚美尼亚</t>
+          <t>印度斯坦</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>步兵和海军文明</t>
+          <t>骆驼和火药文明</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -2330,19 +2525,19 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>步兵和海军文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「骡车费用-25%」）</t>
+          <t>骆驼和火药文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「村民黑暗/封建/城堡/帝王费用-8/13/18/23%」）</t>
         </is>
       </c>
     </row>
     <row r="44" ht="36" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>意大利</t>
+          <t>印加</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>弓兵和海军文明</t>
+          <t>步兵文明</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -2352,19 +2547,19 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>弓兵和海军文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「升时代费用-15%」）</t>
+          <t>步兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「房屋/聚落人口+5」）</t>
         </is>
       </c>
     </row>
     <row r="45" ht="36" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>印度斯坦</t>
+          <t>越南</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>骆驼和火药文明</t>
+          <t>弓兵文明</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -2374,19 +2569,19 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>骆驼和火药文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「村民黑暗/封建/城堡/帝王费用-8/13/18/23%」）</t>
+          <t>弓兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「开局显示敌方TC」）</t>
         </is>
       </c>
     </row>
     <row r="46" ht="36" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>印加</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>步兵文明</t>
+          <t>步弓手和火药文明</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -2396,19 +2591,19 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>步兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「房屋/聚落人口+5」）</t>
+          <t>步弓手和火药文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「初始村民+3，木材-50，食物-200」）</t>
         </is>
       </c>
     </row>
     <row r="47" ht="36" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>越南</t>
+          <t>阿契美尼德</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>弓兵文明</t>
+          <t>弓兵和骑兵文明</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -2418,19 +2613,19 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>弓兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「开局显示敌方TC」）</t>
+          <t>弓兵和骑兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「造船厂工作速度+15%」）</t>
         </is>
       </c>
     </row>
     <row r="48" ht="36" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>中国</t>
+          <t>马其顿人</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>步弓手和火药文明</t>
+          <t>步兵和骑兵文明</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -2440,19 +2635,19 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>步弓手和火药文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「初始村民+3，木材-50，食物-200」）</t>
+          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「高地受伤-10%」）</t>
         </is>
       </c>
     </row>
     <row r="49" ht="36" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>阿契美尼德</t>
+          <t>普鲁人</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>弓兵和骑兵文明</t>
+          <t>弓兵和象兵文明</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -2462,19 +2657,19 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>弓兵和骑兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「造船厂工作速度+15%」）</t>
+          <t>弓兵和象兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「采石村民缓慢获食」）</t>
         </is>
       </c>
     </row>
     <row r="50" ht="36" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>马其顿人</t>
+          <t>色雷斯人</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明</t>
+          <t>步兵文明</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -2484,19 +2679,19 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「高地受伤-10%」）</t>
+          <t>步兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「精锐掷矛手升级免费」）</t>
         </is>
       </c>
     </row>
     <row r="51" ht="36" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>普鲁人</t>
+          <t>斯巴达</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>弓兵和象兵文明</t>
+          <t>步兵文明</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -2506,19 +2701,19 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>弓兵和象兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「采石村民缓慢获食」）</t>
+          <t>步兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「进入市政/古典免费获一军事执政官」）</t>
         </is>
       </c>
     </row>
     <row r="52" ht="36" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>色雷斯人</t>
+          <t>雅典</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>步兵文明</t>
+          <t>步兵和海军文明</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -2528,56 +2723,12 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>步兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「精锐掷矛手升级免费」）</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="36" customHeight="1">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>斯巴达</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>步兵文明</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="inlineStr">
-        <is>
-          <t>无一条直接加强骑射手</t>
-        </is>
-      </c>
-      <c r="D53" s="4" t="inlineStr">
-        <is>
-          <t>步兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「进入市政/古典免费获一军事执政官」）</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="36" customHeight="1">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>雅典</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>步兵和海军文明</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="inlineStr">
-        <is>
-          <t>无一条直接加强骑射手</t>
-        </is>
-      </c>
-      <c r="D54" s="4" t="inlineStr">
-        <is>
           <t>步兵和海军文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「TC可切换政策风格（经济/海军/军事）」）</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D54"/>
+  <autoFilter ref="A1:D52"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -2707,22 +2858,22 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>匈奴</t>
+          <t>土耳其</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>骑射手城堡/帝王费用-10/20%</t>
+          <t>西帕希骑兵（骑射手生命+20）</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1）；骑射手科技树 13/14。缺：环甲</t>
+          <t>原生条目 1 条（强 1）；骑射手科技树 14/14。科技树无缺项</t>
         </is>
       </c>
     </row>
@@ -2732,7 +2883,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>土耳其</t>
+          <t>日本</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -2742,7 +2893,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>西帕希骑兵（骑射手生命+20）</t>
+          <t>骑射手对远程攻+2（掷矛手除外）</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -2757,7 +2908,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>契丹</t>
+          <t>波斯</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -2767,12 +2918,12 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>重装骑射手城堡可升级，成本-50%</t>
+          <t>城堡时代可用帕提亚战术</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1）；骑射手科技树 13/14。缺：血统</t>
+          <t>原生条目 1 条（强 1）；骑射手科技树 13/14。缺：护腕</t>
         </is>
       </c>
     </row>
@@ -2782,22 +2933,22 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>日本</t>
+          <t>库曼</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>12/14</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>骑射手对远程攻+2（掷矛手除外）</t>
+          <t>大草原畜牧（斥候/草原枪兵/骑射手训练速度+100%）</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1）；骑射手科技树 14/14。科技树无缺项</t>
+          <t>原生条目 1 条（强 1）；骑射手科技树 12/14。缺：驯马、护腕</t>
         </is>
       </c>
     </row>
@@ -2807,7 +2958,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>波斯</t>
+          <t>匈奴</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -2817,12 +2968,12 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>城堡时代可用帕提亚战术</t>
+          <t>骑射手城堡/帝王费用-10/20%</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1）；骑射手科技树 13/14。缺：护腕</t>
+          <t>原生条目 1 条（强 1）；骑射手科技树 13/14。缺：环甲</t>
         </is>
       </c>
     </row>
@@ -2832,22 +2983,22 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>库曼</t>
+          <t>契丹</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>大草原畜牧（斥候/草原枪兵/骑射手训练速度+100%）</t>
+          <t>重装骑射手城堡可升级，成本-50%</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1）；骑射手科技树 12/14。缺：驯马、护腕</t>
+          <t>原生条目 1 条（强 1）；骑射手科技树 13/14。缺：血统</t>
         </is>
       </c>
     </row>
@@ -2928,16 +3079,16 @@
       </c>
       <c r="E2" s="8" t="inlineStr">
         <is>
-          <t>骑射手攻速+25%</t>
+          <t>骑射手攻速+25%；斥候/草原枪兵城堡/帝王生命+20/30%</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 1 / 弱 1）；骑射手科技树 13/14；缺 环甲；最直接一条：骑射手攻速+25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 1）；骑射手科技树 13/14；缺 环甲；最直接一条：骑射手攻速+25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="51" customHeight="1">
       <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
@@ -2958,12 +3109,12 @@
       </c>
       <c r="E3" s="8" t="inlineStr">
         <is>
-          <t>反曲弓（骑射手攻+1，射程+1）；骑射手训练速度 +25%</t>
+          <t>科维尼安军队（马扎尔骠骑消耗额外食物而非黄金）；反曲弓（骑射手攻+1，射程+1）；骑射手训练速度 +25%</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 3 / 弱 0）；骑射手科技树 14/14（无缺项）；最直接一条：科维尼安军队（马扎尔骠骑消耗额外食物而非黄金）</t>
+          <t>阶段1·本体强化；原生条目 5 条（强 3 / 弱 0）；骑射手科技树 14/14（无缺项）；最直接一条：科维尼安军队（马扎尔骠骑消耗额外食物而非黄金）</t>
         </is>
       </c>
     </row>
@@ -2988,12 +3139,12 @@
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>扳指/帕提亚战术免费；骑射手视野 +2</t>
+          <t>扳指/帕提亚战术免费；骑射手视野 +2；丝护甲（斥候/草原枪兵近战护甲+1/远程护甲+1）</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 2 / 弱 1）；骑射手科技树 14/14（无缺项）；最直接一条：扳指/帕提亚战术免费</t>
+          <t>阶段1·本体强化；原生条目 5 条（强 2 / 弱 1）；骑射手科技树 14/14（无缺项）；最直接一条：扳指/帕提亚战术免费</t>
         </is>
       </c>
     </row>
@@ -3003,7 +3154,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>匈奴</t>
+          <t>土耳其</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -3018,12 +3169,12 @@
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>骑射手城堡/帝王费用-10/20%</t>
+          <t>西帕希骑兵（骑射手生命+20）</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；骑射手科技树 13/14；缺 环甲；最直接一条：骑射手城堡/帝王费用-10/20%</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；骑射手科技树 14/14（无缺项）；最直接一条：西帕希骑兵（骑射手生命+20）</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3184,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>土耳其</t>
+          <t>日本</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -3048,12 +3199,12 @@
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>西帕希骑兵（骑射手生命+20）</t>
+          <t>骑射手对远程攻+2（掷矛手除外）</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；骑射手科技树 14/14（无缺项）；最直接一条：西帕希骑兵（骑射手生命+20）</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；骑射手科技树 14/14（无缺项）；最直接一条：骑射手对远程攻+2（掷矛手除外）</t>
         </is>
       </c>
     </row>
@@ -3063,7 +3214,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>契丹</t>
+          <t>波斯</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -3078,22 +3229,22 @@
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>重装骑射手城堡可升级，成本-50%</t>
+          <t>城堡时代可用帕提亚战术</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；骑射手科技树 13/14；缺 血统；最直接一条：重装骑射手城堡可升级，成本-50%</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；骑射手科技树 13/14；缺 护腕；最直接一条：城堡时代可用帕提亚战术</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="51" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>日本</t>
+          <t>库曼</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -3108,12 +3259,12 @@
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>骑射手对远程攻+2（掷矛手除外）</t>
+          <t>大草原畜牧（斥候/草原枪兵/骑射手训练速度+100%）</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；骑射手科技树 14/14（无缺项）；最直接一条：骑射手对远程攻+2（掷矛手除外）</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；骑射手科技树 12/14；缺 驯马、护腕；最直接一条：大草原畜牧（斥候/草原枪兵/骑射手训练速度+100%）</t>
         </is>
       </c>
     </row>
@@ -3123,7 +3274,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>波斯</t>
+          <t>匈奴</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -3138,12 +3289,12 @@
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>城堡时代可用帕提亚战术</t>
+          <t>骑射手城堡/帝王费用-10/20%</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；骑射手科技树 13/14；缺 护腕；最直接一条：城堡时代可用帕提亚战术</t>
+          <t>阶段2·减费用；原生条目 2 条（强 1 / 弱 0）；骑射手科技树 13/14；缺 环甲；最直接一条：骑射手城堡/帝王费用-10/20%</t>
         </is>
       </c>
     </row>
@@ -3153,7 +3304,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>库曼</t>
+          <t>契丹</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -3168,12 +3319,12 @@
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>大草原畜牧（斥候/草原枪兵/骑射手训练速度+100%）</t>
+          <t>重装骑射手城堡可升级，成本-50%</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；骑射手科技树 12/14；缺 驯马、护腕；最直接一条：大草原畜牧（斥候/草原枪兵/骑射手训练速度+100%）</t>
+          <t>阶段2·减费用；原生条目 2 条（强 1 / 弱 0）；骑射手科技树 13/14；缺 血统；最直接一条：重装骑射手城堡可升级，成本-50%</t>
         </is>
       </c>
     </row>
@@ -3183,27 +3334,27 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>阿兹特克</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>D</t>
+          <t>高丽</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>不建议</t>
+          <t>2000 金</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>无一条直接加强骑射手</t>
+          <t>弓兵护甲/塔升级免费（升级炮塔需要化学）</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>步兵和僧侣文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「初始黄金+50」）</t>
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；骑射手科技树 12/14；缺 帕提亚战术、血统</t>
         </is>
       </c>
     </row>
@@ -3213,27 +3364,27 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>埃塞俄比亚</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>D</t>
+          <t>葡萄牙</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>不建议</t>
+          <t>2000 金</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>无一条直接加强骑射手</t>
+          <t>所有单位黄金费用-20%</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>弓兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「升时代获得黄金+100、食物+100」）</t>
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；骑射手科技树 11/14；缺 重装骑射手、骑射手、帕提亚战术</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3394,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>柏柏尔</t>
+          <t>阿兹特克</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
@@ -3263,7 +3414,7 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>骑兵和海军文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「村民黑暗移速+5%，封建起+10%」）</t>
+          <t>步兵和僧侣文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「初始黄金+50」）</t>
         </is>
       </c>
     </row>
@@ -3273,7 +3424,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>拜占庭</t>
+          <t>埃塞俄比亚</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
@@ -3293,7 +3444,7 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>防御文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「建筑黑暗/封建/城堡/帝王生命+10/20/30/40%」）</t>
+          <t>弓兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「升时代获得黄金+100、食物+100」）</t>
         </is>
       </c>
     </row>
@@ -3303,7 +3454,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>保加利亚</t>
+          <t>柏柏尔</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
@@ -3323,7 +3474,7 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「民兵系升级免费」）</t>
+          <t>骑兵和海军文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「村民黑暗移速+5%，封建起+10%」）</t>
         </is>
       </c>
     </row>
@@ -3333,7 +3484,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>波兰</t>
+          <t>拜占庭</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
@@ -3353,7 +3504,7 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「大庄园替代磨坊」）</t>
+          <t>防御文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「建筑黑暗/封建/城堡/帝王生命+10/20/30/40%」）</t>
         </is>
       </c>
     </row>
@@ -3363,7 +3514,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>波希米亚</t>
+          <t>保加利亚</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
@@ -3383,7 +3534,7 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>火药和僧侣文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「采矿场科技免费」）</t>
+          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「民兵系升级免费」）</t>
         </is>
       </c>
     </row>
@@ -3393,7 +3544,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>勃艮第</t>
+          <t>波兰</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
@@ -3413,7 +3564,7 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「可提前一个时代经济升级且食物-40%」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「大庄园替代磨坊」）</t>
         </is>
       </c>
     </row>
@@ -3423,7 +3574,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>不列颠</t>
+          <t>波希米亚</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
@@ -3443,7 +3594,7 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>步弓手文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「羊倌工作速度+25%」）</t>
+          <t>火药和僧侣文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「采矿场科技免费」）</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3604,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>达罗毗荼</t>
+          <t>勃艮第</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
@@ -3473,7 +3624,7 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>步兵和海军文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「渔夫/捕鱼船携带+15」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「可提前一个时代经济升级且食物-40%」）</t>
         </is>
       </c>
     </row>
@@ -3483,7 +3634,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>丹麦人</t>
+          <t>不列颠</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
@@ -3503,7 +3654,7 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>步兵和攻城文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「捕鱼船/村民存食+5%」）</t>
+          <t>步弓手文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「羊倌工作速度+25%」）</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3664,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>法兰克</t>
+          <t>达罗毗荼</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
@@ -3533,7 +3684,7 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「采果工速度+15%」）</t>
+          <t>步兵和海军文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「渔夫/捕鱼船携带+15」）</t>
         </is>
       </c>
     </row>
@@ -3543,7 +3694,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>高丽</t>
+          <t>丹麦人</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
@@ -3563,7 +3714,7 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>防御和海军文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「石矿工速度+20%」）</t>
+          <t>步兵和攻城文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「捕鱼船/村民存食+5%」）</t>
         </is>
       </c>
     </row>
@@ -3573,7 +3724,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>高棉</t>
+          <t>法兰克</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
@@ -3593,7 +3744,7 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>攻城武器和大象文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「无需建筑即可升时代/解锁建筑」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「采果工速度+15%」）</t>
         </is>
       </c>
     </row>
@@ -3603,7 +3754,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>哥特</t>
+          <t>高棉</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
@@ -3623,7 +3774,7 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>步兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「可立即研究织布机」）</t>
+          <t>攻城武器和大象文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「无需建筑即可升时代/解锁建筑」）</t>
         </is>
       </c>
     </row>
@@ -3633,7 +3784,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>格鲁吉亚</t>
+          <t>哥特</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
@@ -3653,7 +3804,7 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>防御和骑兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「开局有骡车」）</t>
+          <t>步兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「可立即研究织布机」）</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3814,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>凯尔特</t>
+          <t>格鲁吉亚</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
@@ -3683,7 +3834,7 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>步兵和攻城武器文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「伐木工速度+15%」）</t>
+          <t>防御和骑兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「开局有骡车」）</t>
         </is>
       </c>
     </row>
@@ -3693,7 +3844,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>立陶宛</t>
+          <t>凯尔特</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
@@ -3713,7 +3864,7 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>骑兵和僧侣文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「每座TC食物+100」）</t>
+          <t>步兵和攻城武器文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「伐木工速度+15%」）</t>
         </is>
       </c>
     </row>
@@ -3723,7 +3874,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>罗马</t>
+          <t>立陶宛</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
@@ -3743,7 +3894,7 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「村民收集/建造/修理速度+5%」）</t>
+          <t>骑兵和僧侣文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「每座TC食物+100」）</t>
         </is>
       </c>
     </row>
@@ -3753,7 +3904,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>马来</t>
+          <t>罗马</t>
         </is>
       </c>
       <c r="C30" s="9" t="inlineStr">
@@ -3773,7 +3924,7 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>海军文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「升时代速度+66%」）</t>
+          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「村民收集/建造/修理速度+5%」）</t>
         </is>
       </c>
     </row>
@@ -3783,7 +3934,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>马里</t>
+          <t>马来</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
@@ -3803,7 +3954,7 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>步兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「建筑木材-15%」）</t>
+          <t>海军文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「升时代速度+66%」）</t>
         </is>
       </c>
     </row>
@@ -3813,7 +3964,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>马普切</t>
+          <t>马里</t>
         </is>
       </c>
       <c r="C32" s="9" t="inlineStr">
@@ -3833,7 +3984,7 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>骑兵与反制单位文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「采果工存食+25%」）</t>
+          <t>步兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「建筑木材-15%」）</t>
         </is>
       </c>
     </row>
@@ -3843,7 +3994,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>玛雅</t>
+          <t>马普切</t>
         </is>
       </c>
       <c r="C33" s="9" t="inlineStr">
@@ -3863,7 +4014,7 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>弓兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「开局村民+1，食物-50」）</t>
+          <t>骑兵与反制单位文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「采果工存食+25%」）</t>
         </is>
       </c>
     </row>
@@ -3873,7 +4024,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>孟加拉</t>
+          <t>玛雅</t>
         </is>
       </c>
       <c r="C34" s="9" t="inlineStr">
@@ -3893,7 +4044,7 @@
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>象兵和海军文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「升时代TC产生2村民」）</t>
+          <t>弓兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「开局村民+1，食物-50」）</t>
         </is>
       </c>
     </row>
@@ -3903,7 +4054,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>缅甸</t>
+          <t>孟加拉</t>
         </is>
       </c>
       <c r="C35" s="9" t="inlineStr">
@@ -3923,7 +4074,7 @@
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「伐木场科技免费」）</t>
+          <t>象兵和海军文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「升时代TC产生2村民」）</t>
         </is>
       </c>
     </row>
@@ -3933,7 +4084,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>穆伊斯卡</t>
+          <t>缅甸</t>
         </is>
       </c>
       <c r="C36" s="9" t="inlineStr">
@@ -3953,7 +4104,7 @@
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>弓兵与僧侣文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「升时代黄金-50%」）</t>
+          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「伐木场科技免费」）</t>
         </is>
       </c>
     </row>
@@ -3963,7 +4114,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>女真</t>
+          <t>穆伊斯卡</t>
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr">
@@ -3983,7 +4134,7 @@
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>骑兵和火药文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「猎物/牲畜肉不腐烂」）</t>
+          <t>弓兵与僧侣文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「升时代黄金-50%」）</t>
         </is>
       </c>
     </row>
@@ -3993,7 +4144,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>葡萄牙</t>
+          <t>女真</t>
         </is>
       </c>
       <c r="C38" s="9" t="inlineStr">
@@ -4013,7 +4164,7 @@
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>海军和火药文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「采果工产食+木材」）</t>
+          <t>骑兵和火药文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「猎物/牲畜肉不腐烂」）</t>
         </is>
       </c>
     </row>
@@ -4780,7 +4931,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4899,101 +5050,141 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>① 只看直接作用于骑射手本体、或其前置/费用/产出的条目；</t>
+          <t>本表按用户打法口径分四个阶段排序：先加强要玩的主流派兵种，再减它的资源消耗，最后才补资源效率。</t>
         </is>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1">
-      <c r="A13" s="11" t="inlineStr"/>
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>① 阶段 1 · 本体强化</t>
+        </is>
+      </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>② 泛用条目与兵种类一律剔除（放进「与骑射流无关·可跳过」）；</t>
+          <t>直接加强骑射手本体的条目（攻击/护甲/生命/攻速/射程/移速/回血/数量/生产训练速度/解锁升级等）。这一档最优先。</t>
         </is>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1">
-      <c r="A14" s="11" t="inlineStr"/>
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>② 阶段 2 · 减费用</t>
+        </is>
+      </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>③ 门槛越低、替代成本越高，名次越靠前。</t>
+          <t>降低该兵种及同系兵种（靶场骑射系）生产所需资源的条目：费用/成本 -N%、升级免费、用其它资源替代。</t>
         </is>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1">
-      <c r="A15" s="11" t="inlineStr"/>
-      <c r="B15" s="11" t="inlineStr"/>
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>③ 阶段 3 · 资源效率</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>采集/产出/携带/贸易/人口/经济科技等让主流派更快成型的条目。</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="19" customHeight="1">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>未验证项</t>
+          <t>④ 阶段 4 · 其他相关</t>
         </is>
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>本表的档位与名次为依据「条目文本 + 官方科技树」的经验判断，未逐项实测；与实战不符时以实战为准。</t>
+          <t>其余与本流派相关、但不属于上述三类的条目。</t>
         </is>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t>★ 最重要的一条：别买重复</t>
-        </is>
-      </c>
+      <c r="A17" s="11" t="inlineStr"/>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>主选文明已经自带的加成，不要再用按钮买一遍——一个按钮只能研究一次，重复等于白花 2000 金。</t>
+          <t>同阶段内按「人工权威顺序（实战强度）」再排；泛用条目与兵种类一律剔除（放进「与骑射流无关·可跳过」）。</t>
         </is>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1">
       <c r="A18" s="11" t="inlineStr"/>
-      <c r="B18" s="11" t="inlineStr">
-        <is>
-          <t>正确流程是：先定主选文明（见「主选文明推荐」），再按剩下的缺口挑 3 个免费位。</t>
-        </is>
-      </c>
+      <c r="B18" s="11" t="inlineStr"/>
     </row>
     <row r="19" ht="19" customHeight="1">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>数据来源</t>
+          <t>未验证项</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>用户提供的 62 张文明卡片 PNG（By RemonBo）+ 游戏官方简体中文字串逐条核对。</t>
+          <t>本表的档位与名次为依据「条目文本 + 官方科技树」的经验判断，未逐项实测；与实战不符时以实战为准。</t>
         </is>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1">
-      <c r="A20" s="11" t="inlineStr"/>
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>★ 最重要的一条：别买重复</t>
+        </is>
+      </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>主选文明的科技树数据来自游戏官方 CivTechTrees 的 62 份 JSON。</t>
+          <t>主选文明已经自带的加成，不要再用按钮买一遍——一个按钮只能研究一次，重复等于白花 2000 金。</t>
         </is>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1">
-      <c r="A21" s="11" t="inlineStr">
-        <is>
-          <t>整理</t>
-        </is>
-      </c>
+      <c r="A21" s="11" t="inlineStr"/>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>By RemonBo；本表由 DSH 生成。</t>
+          <t>正确流程是：先定主选文明（见「主选文明推荐」），再按剩下的缺口挑 3 个免费位。</t>
         </is>
       </c>
     </row>
     <row r="22" ht="19" customHeight="1">
       <c r="A22" s="11" t="inlineStr">
         <is>
+          <t>数据来源</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>用户提供的 62 张文明卡片 PNG（By RemonBo）+ 游戏官方简体中文字串逐条核对。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="19" customHeight="1">
+      <c r="A23" s="11" t="inlineStr"/>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>主选文明的科技树数据来自游戏官方 CivTechTrees 的 62 份 JSON。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="19" customHeight="1">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>整理</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>By RemonBo；本表由 DSH 生成。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="19" customHeight="1">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
           <t>与本表配套</t>
         </is>
       </c>
-      <c r="B22" s="11" t="inlineStr">
+      <c r="B25" s="11" t="inlineStr">
         <is>
           <t>同目录下的箭塔流、炮塔流与其余流派总表。</t>
         </is>

--- a/帝国时代2决定版 文明联盟 骑射流最优研究顺序 By RemonBo.xlsx
+++ b/帝国时代2决定版 文明联盟 骑射流最优研究顺序 By RemonBo.xlsx
@@ -18,15 +18,15 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'开局3免费位'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'后续2000金顺序'!$A$1:$F$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'后续2000金顺序'!$A$1:$F$11</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'后续2000金顺序'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'甲类·骑射手本体强化'!$A$1:$E$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'甲类·骑射手本体强化'!$A$1:$E$11</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'甲类·骑射手本体强化'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'乙类·减费用与资源效率'!$A$1:$E$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'乙类·减费用与资源效率'!$A$1:$E$11</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'乙类·减费用与资源效率'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'与骑射流无关·可跳过'!$A$1:$D$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'与骑射流无关·可跳过'!$A$1:$D$50</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'与骑射流无关·可跳过'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'主选文明推荐'!$A$1:$E$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'主选文明推荐'!$A$1:$E$14</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'主选文明推荐'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'全62文明总名次'!$A$1:$F$63</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'全62文明总名次'!$1:$1</definedName>
@@ -622,7 +622,7 @@
       <c r="C5" s="4" t="inlineStr"/>
       <c r="D5" s="4" t="inlineStr"/>
     </row>
-    <row r="6" ht="51" customHeight="1">
+    <row r="6" ht="36" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>第 2 位</t>
@@ -635,7 +635,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>科维尼安军队（马扎尔骠骑消耗额外食物而非黄金）；反曲弓（骑射手攻+1，射程+1）；骑射手训练速度 +25%</t>
+          <t>反曲弓（骑射手攻+1，射程+1）；骑射手训练速度 +25%</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -654,7 +654,7 @@
       <c r="C7" s="4" t="inlineStr"/>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>备选：阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；骑射手科技树 13/14；缺 护腕；最直接一条：城堡时代可用帕提亚战术</t>
+          <t>备选：阶段1·本体强化；原生条目 3 条（强 1 / 弱 1）；骑射手科技树 13/14；缺 护腕；最直接一条：城堡时代可用帕提亚战术</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       <c r="C8" s="4" t="inlineStr"/>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>备选：阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；骑射手科技树 12/14；缺 驯马、护腕；最直接一条：大草原畜牧（斥候/草原枪兵/骑射手训练速度+100%）</t>
+          <t>备选：阶段1·本体强化；原生条目 3 条（强 1 / 弱 1）；骑射手科技树 12/14；缺 驯马、护腕；最直接一条：大草原畜牧（斥候/草原枪兵/骑射手训练速度+100%）</t>
         </is>
       </c>
     </row>
@@ -691,7 +691,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>扳指/帕提亚战术免费；骑射手视野 +2；丝护甲（斥候/草原枪兵近战护甲+1/远程护甲+1）</t>
+          <t>骑射手视野 +2；丝护甲（斥候/草原枪兵近战护甲+1/远程护甲+1）</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -746,7 +746,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -875,7 +875,7 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；骑射手科技树 13/14；缺 护腕；最直接一条：城堡时代可用帕提亚战术</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 1）；骑射手科技树 13/14；缺 护腕；最直接一条：城堡时代可用帕提亚战术</t>
         </is>
       </c>
     </row>
@@ -905,7 +905,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；骑射手科技树 12/14；缺 驯马、护腕；最直接一条：大草原畜牧（斥候/草原枪兵/骑射手训练速度+100%）</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 1）；骑射手科技树 12/14；缺 驯马、护腕；最直接一条：大草原畜牧（斥候/草原枪兵/骑射手训练速度+100%）</t>
         </is>
       </c>
     </row>
@@ -1029,8 +1029,68 @@
         </is>
       </c>
     </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>蜀</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>弓兵靶场/铁匠铺科技-25%</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>无条件</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；骑射手科技树 12/14；缺 帕提亚战术、血统</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>图皮</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>靶场/兵营升级食物-50%</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>无条件</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；骑射手科技树 8/14；缺 重装骑射手、骑射手、帕提亚战术、扳指</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F9"/>
+  <autoFilter ref="A1:F11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -1042,7 +1102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1146,7 +1206,7 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>科维尼安军队（马扎尔骠骑消耗额外食物而非黄金）</t>
+          <t>反曲弓（骑射手攻+1，射程+1）</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1156,7 +1216,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>资源产出/节省，加快成型</t>
+          <t>射程提升</t>
         </is>
       </c>
     </row>
@@ -1173,17 +1233,17 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>反曲弓（骑射手攻+1，射程+1）</t>
+          <t>骑射手训练速度 +25%</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>独特科技</t>
+          <t>团队加成</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>射程提升</t>
+          <t>训练速度提升，成型更快</t>
         </is>
       </c>
     </row>
@@ -1195,12 +1255,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>马扎尔</t>
+          <t>鞑靼</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>骑射手训练速度 +25%</t>
+          <t>骑射手视野 +2</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1210,7 +1270,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>训练速度提升，成型更快</t>
+          <t>视野提升</t>
         </is>
       </c>
     </row>
@@ -1227,71 +1287,71 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>扳指/帕提亚战术免费</t>
+          <t>丝护甲（斥候/草原枪兵近战护甲+1/远程护甲+1）</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>护甲提升，减伤更耐打</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>土耳其</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>西帕希骑兵（骑射手生命+20）</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>生命值提升，抗打更久</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>日本</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>骑射手对远程攻+2（掷矛手除外）</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>免费获得，等于直接省下这笔支出</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>鞑靼</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>骑射手视野 +2</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>团队加成</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>视野提升</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>鞑靼</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>丝护甲（斥候/草原枪兵近战护甲+1/远程护甲+1）</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>护甲提升，减伤更耐打</t>
+          <t>攻击力提升，正面更硬</t>
         </is>
       </c>
     </row>
@@ -1303,22 +1363,22 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>土耳其</t>
+          <t>波斯</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>西帕希骑兵（骑射手生命+20）</t>
+          <t>城堡时代可用帕提亚战术</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>独特科技</t>
+          <t>主要功能</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>生命值提升，抗打更久</t>
+          <t>提前解锁，抢一个时代的节奏</t>
         </is>
       </c>
     </row>
@@ -1330,81 +1390,27 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>日本</t>
+          <t>库曼</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>骑射手对远程攻+2（掷矛手除外）</t>
+          <t>大草原畜牧（斥候/草原枪兵/骑射手训练速度+100%）</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>主要功能</t>
+          <t>独特科技</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>攻击力提升，正面更硬</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>波斯</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>城堡时代可用帕提亚战术</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>提前解锁，抢一个时代的节奏</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>库曼</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>大草原畜牧（斥候/草原枪兵/骑射手训练速度+100%）</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
           <t>训练速度提升，成型更快</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E13"/>
+  <autoFilter ref="A1:E11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -1416,7 +1422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1454,115 +1460,277 @@
       </c>
     </row>
     <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>马扎尔</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>科维尼安军队（马扎尔骠骑消耗额外食物而非黄金）</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>资源产出/节省，加快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>鞑靼</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>扳指/帕提亚战术免费</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>免费获得，等于直接省下这笔支出</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>波斯</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>波斯步弓手（弓兵系消耗额外木材而非黄金）</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>资源产出/节省，加快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>库曼</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>靶场/马厩木材-75</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>资源产出/节省，加快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>匈奴</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>骑射手城堡/帝王费用-10/20%</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>降低费用，让该流派更快成型</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="36" customHeight="1">
-      <c r="A3" s="6" t="inlineStr">
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>契丹</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>重装骑射手城堡可升级，成本-50%</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>解锁额外单位或升级选项，本流派可用的兵种更多</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
+    <row r="8" ht="36" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>高丽</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>弓兵护甲/塔升级免费（升级炮塔需要化学）</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>免费获得整条升级/科技，等于直接省下这笔研究支出</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>葡萄牙</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>所有单位黄金费用-20%</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>降低费用，让该流派更快成型</t>
         </is>
       </c>
     </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>蜀</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>弓兵靶场/铁匠铺科技-25%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>图皮</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>靶场/兵营升级食物-50%</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E5"/>
+  <autoFilter ref="A1:E11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -1574,7 +1742,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D52"/>
+  <dimension ref="A1:D50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2246,12 +2414,12 @@
     <row r="31" ht="36" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>蜀</t>
+          <t>斯拉夫</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>弓兵和攻城文明</t>
+          <t>步兵和攻城文明</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -2261,19 +2429,19 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>弓兵和攻城文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「伐木工产木+食物」）</t>
+          <t>步兵和攻城文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「农民工作速度+15%」）</t>
         </is>
       </c>
     </row>
     <row r="32" ht="36" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>斯拉夫</t>
+          <t>条顿</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>步兵和攻城文明</t>
+          <t>步兵和防御文明</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -2283,19 +2451,19 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>步兵和攻城文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「农民工作速度+15%」）</t>
+          <t>步兵和防御文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「农田费用-40%」）</t>
         </is>
       </c>
     </row>
     <row r="33" ht="36" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>条顿</t>
+          <t>瓦兰吉人</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>步兵和防御文明</t>
+          <t>骑兵和海军文明</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -2305,19 +2473,19 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>步兵和防御文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「农田费用-40%」）</t>
+          <t>骑兵和海军文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「牧羊/捕鱼/狩猎也产黄金」）</t>
         </is>
       </c>
     </row>
     <row r="34" ht="36" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>图皮</t>
+          <t>维京</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>弓兵与步兵文明</t>
+          <t>步兵和海军文明</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -2327,19 +2495,19 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>弓兵与步兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「开局每种资源+25」）</t>
+          <t>步兵和海军文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「独轮推车/手推车免费」）</t>
         </is>
       </c>
     </row>
     <row r="35" ht="36" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>瓦兰吉人</t>
+          <t>魏</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>骑兵和海军文明</t>
+          <t>骑兵文明</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -2349,14 +2517,14 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>骑兵和海军文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「牧羊/捕鱼/狩猎也产黄金」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「每研究一次经济升级免费获一村民」）</t>
         </is>
       </c>
     </row>
     <row r="36" ht="36" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>维京</t>
+          <t>吴</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2371,19 +2539,19 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>步兵和海军文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「独轮推车/手推车免费」）</t>
+          <t>步兵和海军文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「军事建筑/码头建成后食物+55」）</t>
         </is>
       </c>
     </row>
     <row r="37" ht="36" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>魏</t>
+          <t>西班牙</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>骑兵文明</t>
+          <t>火药和僧侣文明</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -2393,19 +2561,19 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「每研究一次经济升级免费获一村民」）</t>
+          <t>火药和僧侣文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「建筑工速度+30%」）</t>
         </is>
       </c>
     </row>
     <row r="38" ht="36" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>吴</t>
+          <t>西西里</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>步兵和海军文明</t>
+          <t>步兵和骑兵文明</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -2415,19 +2583,19 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>步兵和海军文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「军事建筑/码头建成后食物+55」）</t>
+          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「初始石料+100」）</t>
         </is>
       </c>
     </row>
     <row r="39" ht="36" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>西班牙</t>
+          <t>亚美尼亚</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>火药和僧侣文明</t>
+          <t>步兵和海军文明</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -2437,19 +2605,19 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>火药和僧侣文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「建筑工速度+30%」）</t>
+          <t>步兵和海军文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「骡车费用-25%」）</t>
         </is>
       </c>
     </row>
     <row r="40" ht="36" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>西西里</t>
+          <t>意大利</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明</t>
+          <t>弓兵和海军文明</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -2459,19 +2627,19 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「初始石料+100」）</t>
+          <t>弓兵和海军文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「升时代费用-15%」）</t>
         </is>
       </c>
     </row>
     <row r="41" ht="36" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>亚美尼亚</t>
+          <t>印度斯坦</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>步兵和海军文明</t>
+          <t>骆驼和火药文明</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -2481,19 +2649,19 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>步兵和海军文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「骡车费用-25%」）</t>
+          <t>骆驼和火药文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「村民黑暗/封建/城堡/帝王费用-8/13/18/23%」）</t>
         </is>
       </c>
     </row>
     <row r="42" ht="36" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>意大利</t>
+          <t>印加</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>弓兵和海军文明</t>
+          <t>步兵文明</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -2503,19 +2671,19 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>弓兵和海军文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「升时代费用-15%」）</t>
+          <t>步兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「房屋/聚落人口+5」）</t>
         </is>
       </c>
     </row>
     <row r="43" ht="36" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>印度斯坦</t>
+          <t>越南</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>骆驼和火药文明</t>
+          <t>弓兵文明</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -2525,19 +2693,19 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>骆驼和火药文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「村民黑暗/封建/城堡/帝王费用-8/13/18/23%」）</t>
+          <t>弓兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「开局显示敌方TC」）</t>
         </is>
       </c>
     </row>
     <row r="44" ht="36" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>印加</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>步兵文明</t>
+          <t>步弓手和火药文明</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -2547,19 +2715,19 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>步兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「房屋/聚落人口+5」）</t>
+          <t>步弓手和火药文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「初始村民+3，木材-50，食物-200」）</t>
         </is>
       </c>
     </row>
     <row r="45" ht="36" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>越南</t>
+          <t>阿契美尼德</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>弓兵文明</t>
+          <t>弓兵和骑兵文明</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -2569,19 +2737,19 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>弓兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「开局显示敌方TC」）</t>
+          <t>弓兵和骑兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「造船厂工作速度+15%」）</t>
         </is>
       </c>
     </row>
     <row r="46" ht="36" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>中国</t>
+          <t>马其顿人</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>步弓手和火药文明</t>
+          <t>步兵和骑兵文明</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -2591,19 +2759,19 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>步弓手和火药文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「初始村民+3，木材-50，食物-200」）</t>
+          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「高地受伤-10%」）</t>
         </is>
       </c>
     </row>
     <row r="47" ht="36" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>阿契美尼德</t>
+          <t>普鲁人</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>弓兵和骑兵文明</t>
+          <t>弓兵和象兵文明</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -2613,19 +2781,19 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>弓兵和骑兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「造船厂工作速度+15%」）</t>
+          <t>弓兵和象兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「采石村民缓慢获食」）</t>
         </is>
       </c>
     </row>
     <row r="48" ht="36" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>马其顿人</t>
+          <t>色雷斯人</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明</t>
+          <t>步兵文明</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -2635,19 +2803,19 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「高地受伤-10%」）</t>
+          <t>步兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「精锐掷矛手升级免费」）</t>
         </is>
       </c>
     </row>
     <row r="49" ht="36" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>普鲁人</t>
+          <t>斯巴达</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>弓兵和象兵文明</t>
+          <t>步兵文明</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -2657,19 +2825,19 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>弓兵和象兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「采石村民缓慢获食」）</t>
+          <t>步兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「进入市政/古典免费获一军事执政官」）</t>
         </is>
       </c>
     </row>
     <row r="50" ht="36" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>色雷斯人</t>
+          <t>雅典</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>步兵文明</t>
+          <t>步兵和海军文明</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -2679,56 +2847,12 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>步兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「精锐掷矛手升级免费」）</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="36" customHeight="1">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>斯巴达</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>步兵文明</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="inlineStr">
-        <is>
-          <t>无一条直接加强骑射手</t>
-        </is>
-      </c>
-      <c r="D51" s="4" t="inlineStr">
-        <is>
-          <t>步兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「进入市政/古典免费获一军事执政官」）</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="36" customHeight="1">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>雅典</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>步兵和海军文明</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="inlineStr">
-        <is>
-          <t>无一条直接加强骑射手</t>
-        </is>
-      </c>
-      <c r="D52" s="4" t="inlineStr">
-        <is>
           <t>步兵和海军文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「TC可切换政策风格（经济/海军/军事）」）</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D52"/>
+  <autoFilter ref="A1:D50"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -2740,7 +2864,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2923,7 +3047,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1）；骑射手科技树 13/14。缺：护腕</t>
+          <t>原生条目 2 条（强 1）；骑射手科技树 13/14。缺：护腕</t>
         </is>
       </c>
     </row>
@@ -2948,7 +3072,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1）；骑射手科技树 12/14。缺：驯马、护腕</t>
+          <t>原生条目 2 条（强 1）；骑射手科技树 12/14。缺：驯马、护腕</t>
         </is>
       </c>
     </row>
@@ -3002,8 +3126,108 @@
         </is>
       </c>
     </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>高丽</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>12/14</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>弓兵护甲/塔升级免费（升级炮塔需要化学）</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>原生条目 1 条（强 0）；骑射手科技树 12/14。缺：帕提亚战术、血统</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>葡萄牙</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>11/14</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>所有单位黄金费用-20%</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>原生条目 1 条（强 0）；骑射手科技树 11/14。缺：重装骑射手、骑射手、帕提亚战术</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>蜀</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>12/14</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>弓兵靶场/铁匠铺科技-25%</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>原生条目 1 条（强 0）；骑射手科技树 12/14。缺：帕提亚战术、血统</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="36" customHeight="1">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>图皮</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>靶场/兵营升级食物-50%</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>原生条目 1 条（强 0）；骑射手科技树 8/14。缺：重装骑射手、骑射手、帕提亚战术、扳指、血统</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E10"/>
+  <autoFilter ref="A1:E14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -3088,7 +3312,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="51" customHeight="1">
+    <row r="3" ht="36" customHeight="1">
       <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
@@ -3109,7 +3333,7 @@
       </c>
       <c r="E3" s="8" t="inlineStr">
         <is>
-          <t>科维尼安军队（马扎尔骠骑消耗额外食物而非黄金）；反曲弓（骑射手攻+1，射程+1）；骑射手训练速度 +25%</t>
+          <t>反曲弓（骑射手攻+1，射程+1）；骑射手训练速度 +25%</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -3139,7 +3363,7 @@
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>扳指/帕提亚战术免费；骑射手视野 +2；丝护甲（斥候/草原枪兵近战护甲+1/远程护甲+1）</t>
+          <t>骑射手视野 +2；丝护甲（斥候/草原枪兵近战护甲+1/远程护甲+1）</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -3234,7 +3458,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；骑射手科技树 13/14；缺 护腕；最直接一条：城堡时代可用帕提亚战术</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 1）；骑射手科技树 13/14；缺 护腕；最直接一条：城堡时代可用帕提亚战术</t>
         </is>
       </c>
     </row>
@@ -3264,7 +3488,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；骑射手科技树 12/14；缺 驯马、护腕；最直接一条：大草原畜牧（斥候/草原枪兵/骑射手训练速度+100%）</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 1）；骑射手科技树 12/14；缺 驯马、护腕；最直接一条：大草原畜牧（斥候/草原枪兵/骑射手训练速度+100%）</t>
         </is>
       </c>
     </row>
@@ -3394,27 +3618,27 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>阿兹特克</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>D</t>
+          <t>蜀</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>不建议</t>
+          <t>2000 金</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>无一条直接加强骑射手</t>
+          <t>弓兵靶场/铁匠铺科技-25%</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>步兵和僧侣文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「初始黄金+50」）</t>
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；骑射手科技树 12/14；缺 帕提亚战术、血统</t>
         </is>
       </c>
     </row>
@@ -3424,27 +3648,27 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>埃塞俄比亚</t>
-        </is>
-      </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>D</t>
+          <t>图皮</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>不建议</t>
+          <t>2000 金</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>无一条直接加强骑射手</t>
+          <t>靶场/兵营升级食物-50%</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>弓兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「升时代获得黄金+100、食物+100」）</t>
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；骑射手科技树 8/14；缺 重装骑射手、骑射手、帕提亚战术、扳指</t>
         </is>
       </c>
     </row>
@@ -3454,7 +3678,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>柏柏尔</t>
+          <t>阿兹特克</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
@@ -3474,7 +3698,7 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>骑兵和海军文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「村民黑暗移速+5%，封建起+10%」）</t>
+          <t>步兵和僧侣文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「初始黄金+50」）</t>
         </is>
       </c>
     </row>
@@ -3484,7 +3708,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>拜占庭</t>
+          <t>埃塞俄比亚</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
@@ -3504,7 +3728,7 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>防御文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「建筑黑暗/封建/城堡/帝王生命+10/20/30/40%」）</t>
+          <t>弓兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「升时代获得黄金+100、食物+100」）</t>
         </is>
       </c>
     </row>
@@ -3514,7 +3738,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>保加利亚</t>
+          <t>柏柏尔</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
@@ -3534,7 +3758,7 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「民兵系升级免费」）</t>
+          <t>骑兵和海军文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「村民黑暗移速+5%，封建起+10%」）</t>
         </is>
       </c>
     </row>
@@ -3544,7 +3768,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>波兰</t>
+          <t>拜占庭</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
@@ -3564,7 +3788,7 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「大庄园替代磨坊」）</t>
+          <t>防御文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「建筑黑暗/封建/城堡/帝王生命+10/20/30/40%」）</t>
         </is>
       </c>
     </row>
@@ -3574,7 +3798,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>波希米亚</t>
+          <t>保加利亚</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
@@ -3594,7 +3818,7 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>火药和僧侣文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「采矿场科技免费」）</t>
+          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「民兵系升级免费」）</t>
         </is>
       </c>
     </row>
@@ -3604,7 +3828,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>勃艮第</t>
+          <t>波兰</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
@@ -3624,7 +3848,7 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「可提前一个时代经济升级且食物-40%」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「大庄园替代磨坊」）</t>
         </is>
       </c>
     </row>
@@ -3634,7 +3858,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>不列颠</t>
+          <t>波希米亚</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
@@ -3654,7 +3878,7 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>步弓手文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「羊倌工作速度+25%」）</t>
+          <t>火药和僧侣文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「采矿场科技免费」）</t>
         </is>
       </c>
     </row>
@@ -3664,7 +3888,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>达罗毗荼</t>
+          <t>勃艮第</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
@@ -3684,7 +3908,7 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>步兵和海军文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「渔夫/捕鱼船携带+15」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「可提前一个时代经济升级且食物-40%」）</t>
         </is>
       </c>
     </row>
@@ -3694,7 +3918,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>丹麦人</t>
+          <t>不列颠</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
@@ -3714,7 +3938,7 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>步兵和攻城文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「捕鱼船/村民存食+5%」）</t>
+          <t>步弓手文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「羊倌工作速度+25%」）</t>
         </is>
       </c>
     </row>
@@ -3724,7 +3948,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>法兰克</t>
+          <t>达罗毗荼</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
@@ -3744,7 +3968,7 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「采果工速度+15%」）</t>
+          <t>步兵和海军文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「渔夫/捕鱼船携带+15」）</t>
         </is>
       </c>
     </row>
@@ -3754,7 +3978,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>高棉</t>
+          <t>丹麦人</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
@@ -3774,7 +3998,7 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>攻城武器和大象文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「无需建筑即可升时代/解锁建筑」）</t>
+          <t>步兵和攻城文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「捕鱼船/村民存食+5%」）</t>
         </is>
       </c>
     </row>
@@ -3784,7 +4008,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>哥特</t>
+          <t>法兰克</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
@@ -3804,7 +4028,7 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>步兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「可立即研究织布机」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「采果工速度+15%」）</t>
         </is>
       </c>
     </row>
@@ -3814,7 +4038,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>格鲁吉亚</t>
+          <t>高棉</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
@@ -3834,7 +4058,7 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>防御和骑兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「开局有骡车」）</t>
+          <t>攻城武器和大象文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「无需建筑即可升时代/解锁建筑」）</t>
         </is>
       </c>
     </row>
@@ -3844,7 +4068,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>凯尔特</t>
+          <t>哥特</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
@@ -3864,7 +4088,7 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>步兵和攻城武器文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「伐木工速度+15%」）</t>
+          <t>步兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「可立即研究织布机」）</t>
         </is>
       </c>
     </row>
@@ -3874,7 +4098,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>立陶宛</t>
+          <t>格鲁吉亚</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
@@ -3894,7 +4118,7 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>骑兵和僧侣文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「每座TC食物+100」）</t>
+          <t>防御和骑兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「开局有骡车」）</t>
         </is>
       </c>
     </row>
@@ -3904,7 +4128,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>罗马</t>
+          <t>凯尔特</t>
         </is>
       </c>
       <c r="C30" s="9" t="inlineStr">
@@ -3924,7 +4148,7 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「村民收集/建造/修理速度+5%」）</t>
+          <t>步兵和攻城武器文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「伐木工速度+15%」）</t>
         </is>
       </c>
     </row>
@@ -3934,7 +4158,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>马来</t>
+          <t>立陶宛</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
@@ -3954,7 +4178,7 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>海军文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「升时代速度+66%」）</t>
+          <t>骑兵和僧侣文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「每座TC食物+100」）</t>
         </is>
       </c>
     </row>
@@ -3964,7 +4188,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>马里</t>
+          <t>罗马</t>
         </is>
       </c>
       <c r="C32" s="9" t="inlineStr">
@@ -3984,7 +4208,7 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>步兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「建筑木材-15%」）</t>
+          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「村民收集/建造/修理速度+5%」）</t>
         </is>
       </c>
     </row>
@@ -3994,7 +4218,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>马普切</t>
+          <t>马来</t>
         </is>
       </c>
       <c r="C33" s="9" t="inlineStr">
@@ -4014,7 +4238,7 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>骑兵与反制单位文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「采果工存食+25%」）</t>
+          <t>海军文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「升时代速度+66%」）</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4248,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>玛雅</t>
+          <t>马里</t>
         </is>
       </c>
       <c r="C34" s="9" t="inlineStr">
@@ -4044,7 +4268,7 @@
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>弓兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「开局村民+1，食物-50」）</t>
+          <t>步兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「建筑木材-15%」）</t>
         </is>
       </c>
     </row>
@@ -4054,7 +4278,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>孟加拉</t>
+          <t>马普切</t>
         </is>
       </c>
       <c r="C35" s="9" t="inlineStr">
@@ -4074,7 +4298,7 @@
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>象兵和海军文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「升时代TC产生2村民」）</t>
+          <t>骑兵与反制单位文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「采果工存食+25%」）</t>
         </is>
       </c>
     </row>
@@ -4084,7 +4308,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>缅甸</t>
+          <t>玛雅</t>
         </is>
       </c>
       <c r="C36" s="9" t="inlineStr">
@@ -4104,7 +4328,7 @@
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「伐木场科技免费」）</t>
+          <t>弓兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「开局村民+1，食物-50」）</t>
         </is>
       </c>
     </row>
@@ -4114,7 +4338,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>穆伊斯卡</t>
+          <t>孟加拉</t>
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr">
@@ -4134,7 +4358,7 @@
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>弓兵与僧侣文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「升时代黄金-50%」）</t>
+          <t>象兵和海军文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「升时代TC产生2村民」）</t>
         </is>
       </c>
     </row>
@@ -4144,7 +4368,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>女真</t>
+          <t>缅甸</t>
         </is>
       </c>
       <c r="C38" s="9" t="inlineStr">
@@ -4164,7 +4388,7 @@
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>骑兵和火药文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「猎物/牲畜肉不腐烂」）</t>
+          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「伐木场科技免费」）</t>
         </is>
       </c>
     </row>
@@ -4174,7 +4398,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>瞿折罗</t>
+          <t>穆伊斯卡</t>
         </is>
       </c>
       <c r="C39" s="9" t="inlineStr">
@@ -4194,7 +4418,7 @@
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>骑兵和骆驼文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「开局2果树丛」）</t>
+          <t>弓兵与僧侣文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「升时代黄金-50%」）</t>
         </is>
       </c>
     </row>
@@ -4204,7 +4428,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>撒克逊人</t>
+          <t>女真</t>
         </is>
       </c>
       <c r="C40" s="9" t="inlineStr">
@@ -4224,7 +4448,7 @@
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>步兵和防御文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「磨坊/木料/采矿场建成后食物+35，石料+10」）</t>
+          <t>骑兵和火药文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「猎物/牲畜肉不腐烂」）</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4458,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>萨拉森</t>
+          <t>瞿折罗</t>
         </is>
       </c>
       <c r="C41" s="9" t="inlineStr">
@@ -4254,7 +4478,7 @@
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>骆驼和海军文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「市场贸易税仅5%」）</t>
+          <t>骑兵和骆驼文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「开局2果树丛」）</t>
         </is>
       </c>
     </row>
@@ -4264,7 +4488,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>蜀</t>
+          <t>撒克逊人</t>
         </is>
       </c>
       <c r="C42" s="9" t="inlineStr">
@@ -4284,7 +4508,7 @@
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>弓兵和攻城文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「伐木工产木+食物」）</t>
+          <t>步兵和防御文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「磨坊/木料/采矿场建成后食物+35，石料+10」）</t>
         </is>
       </c>
     </row>
@@ -4294,7 +4518,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>斯拉夫</t>
+          <t>萨拉森</t>
         </is>
       </c>
       <c r="C43" s="9" t="inlineStr">
@@ -4314,7 +4538,7 @@
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>步兵和攻城文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「农民工作速度+15%」）</t>
+          <t>骆驼和海军文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「市场贸易税仅5%」）</t>
         </is>
       </c>
     </row>
@@ -4324,7 +4548,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>条顿</t>
+          <t>斯拉夫</t>
         </is>
       </c>
       <c r="C44" s="9" t="inlineStr">
@@ -4344,7 +4568,7 @@
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>步兵和防御文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「农田费用-40%」）</t>
+          <t>步兵和攻城文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「农民工作速度+15%」）</t>
         </is>
       </c>
     </row>
@@ -4354,7 +4578,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>图皮</t>
+          <t>条顿</t>
         </is>
       </c>
       <c r="C45" s="9" t="inlineStr">
@@ -4374,7 +4598,7 @@
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>弓兵与步兵文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「开局每种资源+25」）</t>
+          <t>步兵和防御文明；本表 450 条中无一条直接作用于骑射手。（它最强的一条功能是「农田费用-40%」）</t>
         </is>
       </c>
     </row>
